--- a/daily_matches/job_matches_2026-04-16.xlsx
+++ b/daily_matches/job_matches_2026-04-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Software Engineer III (AI/ML)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Docker, Kubernetes, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11ce688bd126a002</t>
+          <t>https://www.indeed.com/viewjob?jk=556295f00aa1a8a3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Intern</t>
+          <t>Data Architect/Modeler</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UMB Financial Corporation</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
+          <t>RAG, S3, Glue, Athena, Redshift, CI/CD, Terraform, Snowflake, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9383cdfd64b1ba21</t>
+          <t>https://www.indeed.com/viewjob?jk=e10ec33698957c81</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist, Upstream Development</t>
+          <t>I Software Engineer – Agentic AI System</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Copilot, TensorFlow, PyTorch, Azure ML, MLflow, CI/CD, Databricks</t>
+          <t>LLaMA, Prompt Engineering, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78a5b56aee27cd1</t>
+          <t>https://www.indeed.com/viewjob?jk=6ccf85218a75e306</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Migration &amp; Code Generation</t>
+          <t>Senior AI Software Engineer – Agentic AI System</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Kubernetes, CI/CD, Kafka, MySQL, MongoDB, NoSQL, Python</t>
+          <t>LLaMA, Prompt Engineering, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20bc83aea1de83b</t>
+          <t>https://www.indeed.com/viewjob?jk=1365263f5673e988</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Enterprise AI Intern</t>
+          <t>Senior Infrastructure and DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, Redshift, BigQuery, Git, Snowflake, BigQuery</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd3f93640b0f8e6</t>
+          <t>https://www.indeed.com/viewjob?jk=cb732e7f93887b62</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GenAI Data Scientist, Commercial, Supply Chain &amp; Trading</t>
+          <t>Senior Infrastructure and DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Git</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d876ae37ee6f5b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=48d522e316145fcc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SAP Successfactors iXp Intern - AI Software Developer - SUMMER 2026</t>
+          <t>Senior Infrastructure and DevOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d358fdd58499f32</t>
+          <t>https://www.indeed.com/viewjob?jk=a7749a2f7e0fcb46</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architecture Intern</t>
+          <t>AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Smart Data Solutions</t>
+          <t>Goodwin Procter LLP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, EC2, Terraform, Git, PostgreSQL, MySQL, Tableau, Power BI, Quicksight, Python</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d67805e12d384da2</t>
+          <t>https://www.indeed.com/viewjob?jk=42a24ecf6a2ddb8e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate IT Officer, Data and Information Management (Associate Data Engineer)</t>
+          <t>Associate Software Engineer, Billing Workflow</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>World Bank Group</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Data Lake, CI/CD, Databricks, PySpark, Python, SQL, R</t>
+          <t>RAG, Prompt Engineering, Athena, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a40cff6b5df03cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ec4171d11b37aece</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Trading, Investment &amp; Optimization - QuantAI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Docker, AKS, Git, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a02726d78410b5</t>
+          <t>https://www.indeed.com/viewjob?jk=69bdda83744afdf3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Data Infrastructure</t>
+          <t>Jr. Full Stack Developer, Smart Factory Solutions</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Kafka, R</t>
+          <t>RAG, Docker, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,637 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df9f48d9232b00bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, CI/CD, Jenkins, Git, Databricks, Kafka, Hadoop, R, Java</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=deb135bf06a2110e</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Database Automation Developer (contract)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>BNY</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Copilot, AKS, CI/CD, Terraform, Git, MongoDB, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=78a015d8ecbb3c7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ML &amp; AI Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Huntersville, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, NoSQL, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fecd1b0fc18b0931</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Data Engineer 4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>BLOC Resources, LLC</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Copilot, Data Lake, CI/CD, Git, Databricks, NoSQL, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e13379e16ee4b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Data Analyst Senior</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Technology Ventures</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Dataflow, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c86157fedcf8f2c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Frontend Engineer (Angular) – Healthcare SaaS</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Davie, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, S3, CI/CD, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd61450e2dc54ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Data Engineer, Cat Digital Data &amp; AI</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Peoria, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, S3, Kinesis, CI/CD, GitHub Actions, Git, Snowflake, Python, R</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=699bf154d150027f</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SAP NS2 Sr. Cloud Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=534a16e97b1661e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Data Engineer - Data Warehouse Architect</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Databricks, Kafka, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48617c6692425cb2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Inrix</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Git, Kafka, PostgreSQL, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2261c05e20ce1b51</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Deka Research &amp; Development</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Manchester, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, PyTorch, Kafka, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35dec79cbdd7dbc0</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Applied AI, Forward Deployed Machine Learning Engineer - Palo Alto</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Mistral AI</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, LangChain, RAG, Mistral, PyTorch, Python, R</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39fed9348cc8a6f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Sr.AI Native Software Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Intone Networks</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b40f31f0bd4449c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AI Enablement Intern</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>CCC Intelligent Solutions</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Kubernetes, Terraform, Git, Python, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7210af87351f9b29</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Software</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>EchoStar</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Littleton, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Kubernetes, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3459b3d02cc17ca4</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Fabric - Sr Data Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>EXL Service</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=26ded768334cbab7</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Software Engineer - Ford Pro Tech</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, Terraform, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5abfb40b06aadbbd</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Core &amp; Main</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, CI/CD, Databricks, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b5e2495e00e0060d</t>
+          <t>https://www.indeed.com/viewjob?jk=99aa0a766ae6eb0a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-16.xlsx
+++ b/daily_matches/job_matches_2026-04-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III (AI/ML)</t>
+          <t>Senior ML Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Docker, Kubernetes, Git, PostgreSQL</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, LangChain, RAG, LLaMA, Hugging Face, S3, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=556295f00aa1a8a3</t>
+          <t>https://www.indeed.com/viewjob?jk=0ee08a694c71ee91</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Architect/Modeler</t>
+          <t>Software Engineer III - Python AI/ML</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, CI/CD, Terraform, Snowflake, Databricks, Redshift</t>
+          <t>Data Scientist, RAG, S3, Kinesis, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10ec33698957c81</t>
+          <t>https://www.indeed.com/viewjob?jk=6f10776c57396ef8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I Software Engineer – Agentic AI System</t>
+          <t>Software Engineer III – Cloud Platform Engineering - Python / AWS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LLaMA, Prompt Engineering, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
+          <t>RAG, S3, EC2, Data Lake, CI/CD, Jenkins, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ccf85218a75e306</t>
+          <t>https://www.indeed.com/viewjob?jk=bb199efc831c0dc4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer – Agentic AI System</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Red Hat</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LLaMA, Prompt Engineering, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
+          <t>AI Engineer, Data Scientist, RAG, Gemini, Copilot, MLflow, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1365263f5673e988</t>
+          <t>https://www.indeed.com/viewjob?jk=ea65e6049e72fa4a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Infrastructure and DevOps Engineer</t>
+          <t>Software Engineer III - Gen AI, Java Full stack</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, PyTorch, Keras, CI/CD, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb732e7f93887b62</t>
+          <t>https://www.indeed.com/viewjob?jk=407e02536674fcbf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Infrastructure and DevOps Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,112 +661,112 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d522e316145fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1513252d7f11af</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Infrastructure and DevOps Engineer</t>
+          <t>Data Scientist / Advanced Analytics Specialist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Python, SQL, R, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7749a2f7e0fcb46</t>
+          <t>https://www.indeed.com/viewjob?jk=4a2475f489bb4ebe</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>Architect: Enterprise Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Goodwin Procter LLP</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
+          <t>Generative AI, Copilot, CI/CD, Git, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42a24ecf6a2ddb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate Software Engineer, Billing Workflow</t>
+          <t>R&amp;D Firmware Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Santa Rosa, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Athena, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Cortex, CI/CD, Jenkins, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,77 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec4171d11b37aece</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Trading, Investment &amp; Optimization - QuantAI Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Logic, Inc.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Python, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=69bdda83744afdf3</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Jr. Full Stack Developer, Smart Factory Solutions</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Magna International</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Troy, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99aa0a766ae6eb0a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2aa43f8b9bb66da</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-16.xlsx
+++ b/daily_matches/job_matches_2026-04-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior ML Engineer - Agentic AI</t>
+          <t>Graph DBA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, LangChain, RAG, LLaMA, Hugging Face, S3, Docker, Kubernetes</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ee08a694c71ee91</t>
+          <t>https://www.indeed.com/viewjob?jk=c15f03a1274f889c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python AI/ML</t>
+          <t>Graph DBA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Kinesis, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f10776c57396ef8</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b5a8aa7c2f7cd5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III – Cloud Platform Engineering - Python / AWS</t>
+          <t>Graph DBA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Data Lake, CI/CD, Jenkins, Git, NoSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb199efc831c0dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=a0522d81a23e6425</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Graph DBA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Red Hat</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Gemini, Copilot, MLflow, Kubernetes, CI/CD, Git, Python</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea65e6049e72fa4a</t>
+          <t>https://www.indeed.com/viewjob?jk=10fa9278e203e8c7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III - Gen AI, Java Full stack</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, PyTorch, Keras, CI/CD, Git, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, CI/CD, Git, BigQuery</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=407e02536674fcbf</t>
+          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, TensorFlow, PyTorch, XGBoost, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1513252d7f11af</t>
+          <t>https://www.indeed.com/viewjob?jk=9d5eb29e23cd1a19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist / Advanced Analytics Specialist</t>
+          <t>Senior Data Scientist – Professional Tax Group (FP&amp;A)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Python, SQL, R, Hypothesis Testing</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,77 +706,392 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a2475f489bb4ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=0995ebddd15223be</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Architect: Enterprise Data</t>
+          <t>Platform Operations Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, CI/CD, Git, Power BI, Python, SQL, R, Optimization</t>
+          <t>AI Engineer, Generative AI, S3, EC2, Docker, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
+          <t>https://www.indeed.com/viewjob?jk=62bcd4ad2d0bbc62</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R&amp;D Firmware Engineer</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Santa Rosa, CA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Docker, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28609b960ec6853f</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sr Data Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Disney Experiences</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Cortex, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Fairstead</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e07cdac563547591</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CardioOne</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, CI/CD, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Consultant - AI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CCG</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, FAISS, Pinecone, Git, Databricks, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f46f80c9b10c44b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Powder Springs, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8316590563863fa4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Performance Engineer - AI Platforms (PSAP Team)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Red Hat</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>10</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Cortex, CI/CD, Jenkins, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, PyTorch, Kubernetes, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0891259a01408641</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Databricks Data Architect - Consultant</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BluEnt</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MLflow, CI/CD, Terraform, Git, Databricks, PySpark, Kafka, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c12fb6e67e8bda7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Developer Internship</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Git, Kafka, Power BI, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2aa43f8b9bb66da</t>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5ee38c644f00bbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data Analyst</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Dataflow, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d188d776490eefc</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-16.xlsx
+++ b/daily_matches/job_matches_2026-04-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Graph DBA</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Snowflake</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Docker, Kubernetes, Git, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15f03a1274f889c</t>
+          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Graph DBA</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Snowflake</t>
+          <t>Data Scientist, RAG, Data Lake, Kinesis, Docker, Kubernetes, CI/CD, Git, Kafka, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b5a8aa7c2f7cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Graph DBA</t>
+          <t>Software Engineer 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>NAES Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Snowflake</t>
+          <t>LangChain, RAG, LLaMA, Copilot, Prompt Engineering, Docker, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0522d81a23e6425</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6d6b0908a2b7fb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Graph DBA</t>
+          <t>AL/ML Technical Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>sdna global</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Snowflake</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, PySpark, Python, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10fa9278e203e8c7</t>
+          <t>https://www.indeed.com/viewjob?jk=c6515c78621c56d2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Software Engineer, AI Agents &amp; Generative AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Vantor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, CI/CD, Git, BigQuery</t>
+          <t>Generative AI, LangChain, RAG, Gemini, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
+          <t>https://www.indeed.com/viewjob?jk=517f59607c7b8677</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer, AI Agents &amp; Generative AI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Vantor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, TensorFlow, PyTorch, XGBoost, Git, Python</t>
+          <t>Generative AI, LangChain, RAG, Gemini, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,427 +671,42 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d5eb29e23cd1a19</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ea5fef7575bcc5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Professional Tax Group (FP&amp;A)</t>
+          <t>IT Applications Engineer IV, Database</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Kaiser Permanente</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python</t>
+          <t>RAG, Data Lake, Git, Databricks, Tableau, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0995ebddd15223be</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Platform Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Newpage Digital Healthcare solutions</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, S3, EC2, Docker, CI/CD, GitHub Actions, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=62bcd4ad2d0bbc62</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AI Data Scientist</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Spring, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Docker, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=28609b960ec6853f</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Disney Experiences</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Cortex, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Fairstead</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e07cdac563547591</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>CardioOne</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>CO, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Consultant - AI</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CCG</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Copilot, FAISS, Pinecone, Git, Databricks, Power BI, R, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f46f80c9b10c44b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Quality Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Powder Springs, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8316590563863fa4</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Performance Engineer - AI Platforms (PSAP Team)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Red Hat</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Hugging Face, PyTorch, Kubernetes, GitHub Actions, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0891259a01408641</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Databricks Data Architect - Consultant</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>BluEnt</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MLflow, CI/CD, Terraform, Git, Databricks, PySpark, Kafka, SQL, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c12fb6e67e8bda7</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Software Developer Internship</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Spring, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, EC2, Git, Kafka, Power BI, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ee38c644f00bbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Senior Consultant - Data Analyst</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Dataflow, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d188d776490eefc</t>
+          <t>https://www.indeed.com/viewjob?jk=2a7b3c5be82dc98c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-16.xlsx
+++ b/daily_matches/job_matches_2026-04-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>SolidWorks</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>12.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Docker, Kubernetes, Git, PostgreSQL, MySQL, MongoDB</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, Docker, CI/CD, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ddcce261de4223</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>Unissant</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Kinesis, Docker, Kubernetes, CI/CD, Git, Kafka, Python</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Databricks, R, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
+          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer 1</t>
+          <t>Trading, Investment &amp; Optimization - QuantAI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NAES Corporation</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Prompt Engineering, Docker, CI/CD, Git, Python, SQL</t>
+          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6d6b0908a2b7fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8a6e5c65a2d8ba5d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AL/ML Technical Architect</t>
+          <t>Trading, Investment &amp; Optimization - QuantAI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sdna global</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, PySpark, Python, R, Scala</t>
+          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6515c78621c56d2</t>
+          <t>https://www.indeed.com/viewjob?jk=04bb93d772070c3d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Agents &amp; Generative AI</t>
+          <t>Trading, Investment &amp; Optimization - QuantAI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vantor</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, CI/CD, Python, R, Java, Scala</t>
+          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=517f59607c7b8677</t>
+          <t>https://www.indeed.com/viewjob?jk=cbc714a19e6c1ebb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Agents &amp; Generative AI</t>
+          <t>Trading, Investment &amp; Optimization - QuantAI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vantor</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, CI/CD, Python, R, Java, Scala</t>
+          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ea5fef7575bcc5</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d2dfd6373f16c8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IT Applications Engineer IV, Database</t>
+          <t>Trading, Investment &amp; Optimization - QuantAI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kaiser Permanente</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,192 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Git, Databricks, Tableau, Power BI, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a7b3c5be82dc98c</t>
+          <t>https://www.indeed.com/viewjob?jk=e084b16c556e5f19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Trading, Investment &amp; Optimization - QuantAI Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d02bf32e84c638e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Trading, Investment &amp; Optimization - QuantAI Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f9cd0af0e96d9ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Trading, Investment &amp; Optimization - QuantAI Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Culver City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e52ec7da9b82ca61</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Trading, Investment &amp; Optimization - QuantAI Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68efd4386bb58a32</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SolidWorks</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Waltham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Docker, CI/CD, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6622ed69cb516901</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-16.xlsx
+++ b/daily_matches/job_matches_2026-04-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Sr Data Scientist - Gen AI ML - Irving</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SolidWorks</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.2</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, FastAPI, Docker, CI/CD, GitHub Actions, Git, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ddcce261de4223</t>
+          <t>https://www.indeed.com/viewjob?jk=b7f2473ba4deec16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Scientist - Gen AI ML - Tampa/Irving/ Mississauga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unissant</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Databricks, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
+          <t>https://www.indeed.com/viewjob?jk=017aeeb1d76aa904</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Trading, Investment &amp; Optimization - QuantAI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Python, R, Java, Optimization</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, MLflow, Docker, Kubernetes, AKS, CI/CD, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a6e5c65a2d8ba5d</t>
+          <t>https://www.indeed.com/viewjob?jk=cb1eb66e038f22b4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Trading, Investment &amp; Optimization - QuantAI Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Python, R, Java, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Docker, Kafka, Hadoop, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04bb93d772070c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=7bdc2a9ca46b0017</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Trading, Investment &amp; Optimization - QuantAI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Python, R, Java, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Synapse, Docker, Kubernetes, Git, Databricks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbc714a19e6c1ebb</t>
+          <t>https://www.indeed.com/viewjob?jk=9f48f4ca79582813</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Trading, Investment &amp; Optimization - QuantAI Engineer</t>
+          <t>Senior Machine Learning Engineer- Credit Karma</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Python, R, Java, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Dataflow, Kubernetes, Databricks, Dask, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d2dfd6373f16c8</t>
+          <t>https://www.indeed.com/viewjob?jk=3002eff397dd1b85</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Trading, Investment &amp; Optimization - QuantAI Engineer</t>
+          <t>Search Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Python, R, Java, Optimization</t>
+          <t>LangChain, RAG, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e084b16c556e5f19</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f16e40fe393829</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Trading, Investment &amp; Optimization - QuantAI Engineer</t>
+          <t>ML Search Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Python, R, Java, Optimization</t>
+          <t>LangChain, RAG, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02bf32e84c638e2</t>
+          <t>https://www.indeed.com/viewjob?jk=c449a720764abe39</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Trading, Investment &amp; Optimization - QuantAI Engineer</t>
+          <t>Senior .NET Developer (Application Modernization / AI Transformation)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>eClerx</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Python, R, Java, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, TensorFlow, PyTorch, CI/CD, Python, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f9cd0af0e96d9ec</t>
+          <t>https://www.indeed.com/viewjob?jk=eac3d2aaefeaa2b1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Trading, Investment &amp; Optimization - QuantAI Engineer</t>
+          <t>Marketing Data Engineer (Digital Marketing Specialist)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Indiana University</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Bloomington, IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Python, R, Java, Optimization</t>
+          <t>RAG, Gemini, Copilot, BigQuery, Git, BigQuery, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52ec7da9b82ca61</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9b1a0df1fee2a9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Trading, Investment &amp; Optimization - QuantAI Engineer</t>
+          <t>Software Engineer 1 - Fullstack</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, FastAPI, Docker, CI/CD, Python, R, Java, Optimization</t>
+          <t>Data Scientist, RAG, S3, CI/CD, Git, R, Java, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,42 +846,147 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68efd4386bb58a32</t>
+          <t>https://www.indeed.com/viewjob?jk=0a98fc4a9d87cedf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SolidWorks</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89d5f2da2c151aea</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Vforce Infotech</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Edison, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, LLaMA, Docker, CI/CD, GitHub Actions, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6622ed69cb516901</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0603d4af22fe6162</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior SRE I</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Waystar</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Apache Airflow, CI/CD, Terraform, Kafka, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=389e6808cb55dd7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Veeva Systems</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, Kinesis, CI/CD, Jenkins, Databricks, Kafka, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a83dccf18841adf6</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-16.xlsx
+++ b/daily_matches/job_matches_2026-04-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - Gen AI ML - Irving</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow</t>
+          <t>S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7f2473ba4deec16</t>
+          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist - Gen AI ML - Tampa/Irving/ Mississauga</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, MySQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=017aeeb1d76aa904</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f81856c387866b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, MLflow, Docker, Kubernetes, AKS, CI/CD, Git</t>
+          <t>Data Scientist, RAG, MLflow, CI/CD, Terraform, Git, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb1eb66e038f22b4</t>
+          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Solution Engineer: Enterprise GenAI &amp; Analytics Enablement</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Docker, Kafka, Hadoop, MongoDB, NoSQL</t>
+          <t>Data Scientist, RAG, MLflow, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bdc2a9ca46b0017</t>
+          <t>https://www.indeed.com/viewjob?jk=ed80186b477d6765</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>IT Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Synapse, Docker, Kubernetes, Git, Databricks</t>
+          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f48f4ca79582813</t>
+          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer- Credit Karma</t>
+          <t>IT Intern - Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Dataflow, Kubernetes, Databricks, Dask, Python, SQL</t>
+          <t>Data Scientist, Generative AI, Copilot, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3002eff397dd1b85</t>
+          <t>https://www.indeed.com/viewjob?jk=9b0bf80c71747171</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Search Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>Data Scientist, RAG, CI/CD, Jenkins, Git, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f16e40fe393829</t>
+          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ML Search Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>hudu</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c449a720764abe39</t>
+          <t>https://www.indeed.com/viewjob?jk=f82ad083945f22d1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior .NET Developer (Application Modernization / AI Transformation)</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>eClerx</t>
+          <t>INFINITE ELECTRONICS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, TensorFlow, PyTorch, CI/CD, Python, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, FastAPI, Docker, CI/CD, PySpark, Python, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac3d2aaefeaa2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=929c65bb94ca47fe</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marketing Data Engineer (Digital Marketing Specialist)</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Indiana University</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bloomington, IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, BigQuery, Git, BigQuery, Tableau, Power BI, Python, SQL</t>
+          <t>RAG, LLaMA, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9b1a0df1fee2a9</t>
+          <t>https://www.indeed.com/viewjob?jk=1498013d4b56a44c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer 1 - Fullstack</t>
+          <t>Senior Site Reliability Engineer, Database</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Airwallex</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, CI/CD, Git, R, Java, Scala, Optimization, A/B Testing</t>
+          <t>Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a98fc4a9d87cedf</t>
+          <t>https://www.indeed.com/viewjob?jk=25fd2fb72d83adb4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Site Reliability Engineer, Database</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Airwallex</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, Git, Kafka, Python, R, Java, Scala</t>
+          <t>Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d5f2da2c151aea</t>
+          <t>https://www.indeed.com/viewjob?jk=77d3f309948626f0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Engineer II, Software</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, S3, CI/CD, Git, Snowflake, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0603d4af22fe6162</t>
+          <t>https://www.indeed.com/viewjob?jk=a025f4feb9304fb1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior SRE I</t>
+          <t>Software Engineer Senior DevOps Azure Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Intermountain Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Murray, UT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Apache Airflow, CI/CD, Terraform, Kafka, Python, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,42 +951,322 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389e6808cb55dd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=ae2c3d722369e270</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Veeva Systems</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, CI/CD, Git, R, Java, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=743639220ad7c9c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DocuSign</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, CI/CD, Git, R, Java, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c76ceabcacd8d819</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, GitHub Actions, Git, Kafka, MongoDB, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow: Generative AI for Protein Engineering</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pfizer</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Groton, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8126a0f70b8ae41</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer 1 (Hybrid Position)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Summit Credit Union</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Cottage Grove, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0182618f5b1f4b4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>GTM Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>GAMMA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a1ebe95a84b136f</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure and Build Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bd40869b37f95ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior AI Defense Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>WilmerHale</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Miamisburg, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, Kubernetes, AKS, CI/CD, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48f904bfd0a7ecec</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Platform Data Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Geisinger</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D24" t="n">
         <v>10</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Data Scientist, Kinesis, CI/CD, Jenkins, Databricks, Kafka, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a83dccf18841adf6</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Pinecone, Databricks, PySpark, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8284b4131a931392</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-16.xlsx
+++ b/daily_matches/job_matches_2026-04-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior AI Engineer for Banking Technology</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Python</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
+          <t>https://www.indeed.com/viewjob?jk=433fa5bd4f34a8f4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, MySQL, NoSQL, Python, SQL</t>
+          <t>LangChain, Prompt Engineering, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f81856c387866b</t>
+          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HR -Data Scientist</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MLflow, CI/CD, Terraform, Git, Tableau, Power BI, Python, SQL</t>
+          <t>LangChain, Prompt Engineering, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
+          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Solution Engineer: Enterprise GenAI &amp; Analytics Enablement</t>
+          <t>Senior Data Engineer - SDE 26-04140</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MLflow, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, RAG, S3, Data Lake, CI/CD, Jenkins, Git, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed80186b477d6765</t>
+          <t>https://www.indeed.com/viewjob?jk=d98bfdf8c981815d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IT Intern - Data Engineer</t>
+          <t>Senior Data Engineer - SDE 26-04140</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL</t>
+          <t>Data Scientist, RAG, S3, Data Lake, CI/CD, Jenkins, Git, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
+          <t>https://www.indeed.com/viewjob?jk=08b278bfb38191e0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IT Intern - Data Scientist</t>
+          <t>Senior Data Engineer - SDE 26-04140</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Copilot, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL</t>
+          <t>Data Scientist, RAG, S3, Data Lake, CI/CD, Jenkins, Git, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b0bf80c71747171</t>
+          <t>https://www.indeed.com/viewjob?jk=f397f88e84805b3d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Data Engineer - SDE 26-04140</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Jenkins, Git, Snowflake, Databricks, Python, SQL, R</t>
+          <t>Data Scientist, RAG, S3, Data Lake, CI/CD, Jenkins, Git, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
+          <t>https://www.indeed.com/viewjob?jk=6b89ceef5f047ae5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Remote Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hudu</t>
+          <t>Astronaut Party Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R</t>
+          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, MongoDB, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82ad083945f22d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Data Scientist - Supply Chain</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>INFINITE ELECTRONICS</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, FastAPI, Docker, CI/CD, PySpark, Python, R, Scala</t>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, CI/CD, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929c65bb94ca47fe</t>
+          <t>https://www.indeed.com/viewjob?jk=8324b1e768293618</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>Senior Data Analyst, Product Support</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Bullhorn</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1498013d4b56a44c</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8370d68b6b20f4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Database</t>
+          <t>Sr. Eng., Eng Services</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>LangChain, RAG, S3, Athena, CI/CD, Jenkins, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25fd2fb72d83adb4</t>
+          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Database</t>
+          <t>Engineer, AI/ML</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>LangChain, RAG, Prompt Engineering, Cortex, AWS SageMaker, S3, AKS, CI/CD, Snowflake, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77d3f309948626f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3164bc8de1c25dac</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Engineer II, Software</t>
+          <t>Data Engineer - Supply Chain</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, CI/CD, Git, Snowflake, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, RAG, CI/CD, Snowflake, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a025f4feb9304fb1</t>
+          <t>https://www.indeed.com/viewjob?jk=b7d88df04613b8f1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer Senior DevOps Azure Platform</t>
+          <t>AI Cloud Engineer (contract)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Intermountain Health</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Murray, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R, Java</t>
+          <t>RAG, Prompt Engineering, AWS SageMaker, S3, EC2, Kubernetes, CI/CD, Terraform, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae2c3d722369e270</t>
+          <t>https://www.indeed.com/viewjob?jk=22a1b966bdbdd4a2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Scientist - Supply Chain</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, CI/CD, Git, R, Java, Scala, Optimization, A/B Testing</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=743639220ad7c9c6</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c384ae5d7d2aac</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer - Applied AI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, CI/CD, Git, R, Java, Scala, Optimization, A/B Testing</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76ceabcacd8d819</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4fe21a770cba88</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Sorcero</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, GitHub Actions, Git, Kafka, MongoDB, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, PyTorch, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
+          <t>https://www.indeed.com/viewjob?jk=7704515258948b02</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Postdoctoral Fellow: Generative AI for Protein Engineering</t>
+          <t>Mid-Level Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>USAA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Groton, CT, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Optimization, Bayesian</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, NoSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8126a0f70b8ae41</t>
+          <t>https://www.indeed.com/viewjob?jk=910d737123428080</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer 1 (Hybrid Position)</t>
+          <t>Senior Full Stack Engineer (Python, Serverless, AI Fluency)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Summit Credit Union</t>
+          <t>VYNYL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cottage Grove, WI, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>Copilot, Kinesis, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0182618f5b1f4b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=81b06e48586c2f5b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GTM Engineer</t>
+          <t>Senior Full Stack Engineer (Python, Serverless, AI Fluency)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GAMMA</t>
+          <t>VYNYL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+          <t>Copilot, Kinesis, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a1ebe95a84b136f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b81304e760b0f5a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Infrastructure and Build Systems Engineer</t>
+          <t>Senior Full Stack Engineer (Python, Serverless, AI Fluency)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>VYNYL</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Copilot, Kinesis, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd40869b37f95ff</t>
+          <t>https://www.indeed.com/viewjob?jk=904e4b3e73f04e6b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AI Defense Engineer</t>
+          <t>Senior Full Stack Engineer (Python, Serverless, AI Fluency)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WilmerHale</t>
+          <t>VYNYL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Miamisburg, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, Kubernetes, AKS, CI/CD, R</t>
+          <t>Copilot, Kinesis, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f904bfd0a7ecec</t>
+          <t>https://www.indeed.com/viewjob?jk=1ef76918623235d2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Platform Data Engineer</t>
+          <t>Senior Full Stack Engineer (Python, Serverless, AI Fluency)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Geisinger</t>
+          <t>VYNYL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Pinecone, Databricks, PySpark, Kafka, Python, SQL, R</t>
+          <t>Copilot, Kinesis, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,217 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8284b4131a931392</t>
+          <t>https://www.indeed.com/viewjob?jk=09c9f5782f15fed9</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LangChain, Prompt Engineering, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0aa03ebbf7563fc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (Python, Serverless, AI Fluency)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>VYNYL</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Copilot, Kinesis, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0659cf046a68568</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Engineer, Data Platform &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, S3, Data Lake, Snowflake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>EXL Service</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fc980fc549b4287</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Generative AI, FastAPI, Jenkins, Git, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64a095dcf458cfe8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Generative AI, FastAPI, Jenkins, Git, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=244b79fa8ae77a3c</t>
         </is>
       </c>
     </row>
